--- a/outputs/05_benchmark_signals/tables_v_viii/us/table_vi_forecast_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/us/table_vi_forecast_logit.xlsx
@@ -442,17 +442,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>0.05 (1.3)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.00 (-1.0)</t>
+          <t>-0.03 (-0.9)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.00*** (6.2)</t>
+          <t>0.22*** (6.2)</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.00*** (14.2)</t>
+          <t>0.51*** (15.2)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.00*** (-16.8)</t>
+          <t>-0.77*** (-16.0)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.1)</t>
+          <t>-0.31*** (-6.1)</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.00*** (-7.4)</t>
+          <t>0.29*** (6.2)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.00*** (-9.7)</t>
+          <t>0.10** (2.0)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.00*** (-12.2)</t>
+          <t>-0.02 (-0.3)</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.00*** (7.3)</t>
+          <t>0.61*** (7.6)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.00*** (7.4)</t>
+          <t>0.69*** (7.7)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00*** (5.0)</t>
+          <t>0.45*** (4.9)</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.11* (1.7)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>0.15** (2.4)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00*** (4.6)</t>
+          <t>0.26*** (4.7)</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.00*** (-9.8)</t>
+          <t>-0.51*** (-10.0)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.00*** (-20.2)</t>
+          <t>-1.19*** (-21.4)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.00*** (-17.0)</t>
+          <t>-1.12*** (-16.8)</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.00*** (-7.1)</t>
+          <t>-0.30*** (-6.9)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.00*** (10.7)</t>
+          <t>0.44*** (10.3)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.00*** (31.7)</t>
+          <t>2.04*** (33.4)</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.00*** (22.8)</t>
+          <t>1.68*** (23.1)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.00*** (24.7)</t>
+          <t>2.83*** (25.6)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.00*** (23.8)</t>
+          <t>2.37*** (23.2)</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.00*** (-18.9)</t>
+          <t>-0.70*** (-21.2)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.00*** (-18.9)</t>
+          <t>-0.86*** (-21.2)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.00*** (-22.6)</t>
+          <t>-0.91*** (-22.7)</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.07 (1.1)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.15*** (2.7)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>-0.02 (-0.4)</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.00*** (17.4)</t>
+          <t>1.61*** (18.0)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.00*** (20.1)</t>
+          <t>2.53*** (21.6)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.00*** (14.3)</t>
+          <t>1.58*** (14.3)</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-0.00*** (-28.1)</t>
+          <t>-1.68*** (-39.0)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.00*** (-26.4)</t>
+          <t>-1.83*** (-36.5)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.00*** (-29.9)</t>
+          <t>-1.80*** (-35.5)</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.58</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.395292413766447e-06</v>
+        <v>0.05046675197156754</v>
       </c>
       <c r="C2" t="n">
-        <v>-6.205780873184355e-06</v>
+        <v>-0.02687696427982563</v>
       </c>
       <c r="D2" t="n">
-        <v>4.787086173543516e-05</v>
+        <v>0.2231192238270082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9924937138975283</v>
+        <v>1.276386946528842</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9836578213852382</v>
+        <v>-0.9275079413863428</v>
       </c>
       <c r="G2" t="n">
-        <v>6.248884969372657</v>
+        <v>6.210175484937285</v>
       </c>
     </row>
     <row r="3">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001093892851462433</v>
+        <v>0.5058700900111862</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.000162740771654804</v>
+        <v>-0.7723037894156176</v>
       </c>
       <c r="D3" t="n">
-        <v>-6.633247866655214e-05</v>
+        <v>-0.3146701679015412</v>
       </c>
       <c r="E3" t="n">
-        <v>14.23826206346421</v>
+        <v>15.20243496960857</v>
       </c>
       <c r="F3" t="n">
-        <v>-16.83922895170482</v>
+        <v>-15.99261588914323</v>
       </c>
       <c r="G3" t="n">
-        <v>-6.144005690208662</v>
+        <v>-6.096503019993369</v>
       </c>
     </row>
     <row r="4">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0001416267524587242</v>
+        <v>0.2868423407955251</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0002278594837309368</v>
+        <v>0.1046050829213526</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0002607209473728548</v>
+        <v>-0.01556710765894723</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.379495908780768</v>
+        <v>6.185746777758568</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.716243736375906</v>
+        <v>1.976518720117358</v>
       </c>
       <c r="G4" t="n">
-        <v>-12.24228724159101</v>
+        <v>-0.2873483626624115</v>
       </c>
     </row>
     <row r="5">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001355160185934424</v>
+        <v>0.6120108538764135</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001529718127112787</v>
+        <v>0.6934035681343207</v>
       </c>
       <c r="D5" t="n">
-        <v>9.708616899029697e-05</v>
+        <v>0.4493895887022047</v>
       </c>
       <c r="E5" t="n">
-        <v>7.316129867459435</v>
+        <v>7.574866409485455</v>
       </c>
       <c r="F5" t="n">
-        <v>7.404433393819633</v>
+        <v>7.66156641404307</v>
       </c>
       <c r="G5" t="n">
-        <v>5.007789692090814</v>
+        <v>4.938277081724165</v>
       </c>
     </row>
     <row r="6">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.689403450028178e-05</v>
+        <v>0.1093811792295117</v>
       </c>
       <c r="C6" t="n">
-        <v>3.304105114634759e-05</v>
+        <v>0.1502464321808525</v>
       </c>
       <c r="D6" t="n">
-        <v>5.288604900355165e-05</v>
+        <v>0.2569797297127046</v>
       </c>
       <c r="E6" t="n">
-        <v>1.92028001411386</v>
+        <v>1.700750348340221</v>
       </c>
       <c r="F6" t="n">
-        <v>2.539581147545954</v>
+        <v>2.424446363281209</v>
       </c>
       <c r="G6" t="n">
-        <v>4.593880365377667</v>
+        <v>4.705079371749331</v>
       </c>
     </row>
     <row r="7">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001091558086580207</v>
+        <v>-0.5067015217546145</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002556156489706176</v>
+        <v>-1.194441250693421</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0002366021057113134</v>
+        <v>-1.115870250301089</v>
       </c>
       <c r="E7" t="n">
-        <v>-9.787989964825682</v>
+        <v>-9.965651341819504</v>
       </c>
       <c r="F7" t="n">
-        <v>-20.1911602718747</v>
+        <v>-21.37072781072958</v>
       </c>
       <c r="G7" t="n">
-        <v>-17.04907726936943</v>
+        <v>-16.79746754158642</v>
       </c>
     </row>
     <row r="8">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-6.293562543872026e-05</v>
+        <v>-0.3037767959606809</v>
       </c>
       <c r="C8" t="n">
-        <v>9.343019738887517e-05</v>
+        <v>0.4412794793356361</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004351848866670693</v>
+        <v>2.041920339623905</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.072155657067622</v>
+        <v>-6.864390417055456</v>
       </c>
       <c r="F8" t="n">
-        <v>10.68015947290596</v>
+        <v>10.2817887360366</v>
       </c>
       <c r="G8" t="n">
-        <v>31.67692636617836</v>
+        <v>33.44262967304867</v>
       </c>
     </row>
     <row r="9">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0003584341792307074</v>
+        <v>1.683687731757687</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0006016325767028924</v>
+        <v>2.827794004212661</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0005019986679335281</v>
+        <v>2.369055379990375</v>
       </c>
       <c r="E9" t="n">
-        <v>22.81683527234107</v>
+        <v>23.1030737784807</v>
       </c>
       <c r="F9" t="n">
-        <v>24.70903196251277</v>
+        <v>25.61843360749334</v>
       </c>
       <c r="G9" t="n">
-        <v>23.79333870599536</v>
+        <v>23.15029975742862</v>
       </c>
     </row>
     <row r="10">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0003500379571628334</v>
+        <v>-0.6964468255603201</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0004328514170908147</v>
+        <v>-0.8627625843146707</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0004512009769495485</v>
+        <v>-0.9095255563541382</v>
       </c>
       <c r="E10" t="n">
-        <v>-18.86194050757961</v>
+        <v>-21.17839239226444</v>
       </c>
       <c r="F10" t="n">
-        <v>-18.86356334053469</v>
+        <v>-21.19415658641432</v>
       </c>
       <c r="G10" t="n">
-        <v>-22.56223578443274</v>
+        <v>-22.65359166052593</v>
       </c>
     </row>
     <row r="11">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.478152602849652e-05</v>
+        <v>0.06639828727608196</v>
       </c>
       <c r="C11" t="n">
-        <v>3.354114574322415e-05</v>
+        <v>0.147531852995433</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.88199650543541e-06</v>
+        <v>-0.02188320655517594</v>
       </c>
       <c r="E11" t="n">
-        <v>1.181715500597107</v>
+        <v>1.139608517838751</v>
       </c>
       <c r="F11" t="n">
-        <v>2.782397044429779</v>
+        <v>2.650390168994072</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5116412192954815</v>
+        <v>-0.3600229091678781</v>
       </c>
     </row>
     <row r="12">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.000343569608993549</v>
+        <v>1.610185932018774</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0005409312968145466</v>
+        <v>2.531261201993108</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0003327907153736284</v>
+        <v>1.583301996171631</v>
       </c>
       <c r="E12" t="n">
-        <v>17.35253647771738</v>
+        <v>17.96543689379004</v>
       </c>
       <c r="F12" t="n">
-        <v>20.05923522098524</v>
+        <v>21.5873378685853</v>
       </c>
       <c r="G12" t="n">
-        <v>14.25291241865725</v>
+        <v>14.31304006832368</v>
       </c>
     </row>
     <row r="13">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.0005584491618669443</v>
+        <v>-1.679735991916152</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.000637843350450696</v>
+        <v>-1.830130251550677</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0006416810065262443</v>
+        <v>-1.80348400504934</v>
       </c>
       <c r="E13" t="n">
-        <v>-28.08662030861234</v>
+        <v>-39.01939465856459</v>
       </c>
       <c r="F13" t="n">
-        <v>-26.3792527797233</v>
+        <v>-36.51686959329967</v>
       </c>
       <c r="G13" t="n">
-        <v>-29.90239096978166</v>
+        <v>-35.47911921217754</v>
       </c>
     </row>
     <row r="14">
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.386243949150183</v>
+        <v>6.439636269865634</v>
       </c>
       <c r="C14" t="n">
-        <v>5.340735897867521</v>
+        <v>5.377486327877346</v>
       </c>
       <c r="D14" t="n">
-        <v>9.555722256293631</v>
+        <v>9.579801684093825</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>

--- a/outputs/05_benchmark_signals/tables_v_viii/us/table_vi_forecast_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/us/table_vi_forecast_logit.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display_stars" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -731,6 +732,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>5D5P</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>20D5P</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>60D5P</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MOM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.22***</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.51***</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-0.77***</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-0.31***</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WSTR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.29***</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.10**</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TREND</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.61***</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.69***</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.45***</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.11*</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.15**</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.26***</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Volat.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-0.51***</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-1.19***</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-1.12***</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>52WH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-0.30***</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.44***</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.04***</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dollar Volume</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.68***</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2.83***</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.37***</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Zero Trade</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-0.70***</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-0.86***</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-0.91***</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.15***</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Illiq.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.61***</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.53***</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.58***</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lag Weekly Return</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>-1.68***</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-1.83***</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-1.80***</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>McFadden R²</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6.44</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9.58</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
